--- a/backend/media/reports/Presence_Genie_Informatique___S5___2026_Compilation_2026-10-28.xlsx
+++ b/backend/media/reports/Presence_Genie_Informatique___S5___2026_Compilation_2026-10-28.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+        <bgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,11 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,18 +440,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,6 +498,96 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M12345678</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>TALIBI</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ABDERRAHIM</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Genie Informatique - S5 - 2026-2027</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Compilation</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ali bekri</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>19:33:55</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Présent</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>M134578sS2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ben</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>farid</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Genie Informatique - S5 - 2026-2027</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Compilation</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>ali bekri</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
